--- a/data/trans_camb/P1_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P1_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,49; -0,14</t>
+          <t>-4,53; -0,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 6,68</t>
+          <t>0,13; 6,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 6,35</t>
+          <t>-2,88; 6,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,06; 4,68</t>
+          <t>0,11; 4,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,9; 8,56</t>
+          <t>2,8; 8,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 6,41</t>
+          <t>0,49; 6,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 1,48</t>
+          <t>-1,7; 1,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,29; 6,71</t>
+          <t>2,35; 6,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 4,34</t>
+          <t>-0,57; 5,23</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-87,23; 0,18</t>
+          <t>-87,08; 1,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 253,21</t>
+          <t>-2,78; 255,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-66,26; 225,26</t>
+          <t>-64,8; 269,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 500,39</t>
+          <t>-6,73; 433,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>94,73; 806,16</t>
+          <t>93,72; 869,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 568,84</t>
+          <t>10,0; 550,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-44,55; 73,23</t>
+          <t>-48,71; 71,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>65,17; 327,38</t>
+          <t>59,94; 326,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-21,3; 201,67</t>
+          <t>-20,58; 224,34</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 5,9</t>
+          <t>0,01; 6,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 7,11</t>
+          <t>0,49; 6,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,61; 14,51</t>
+          <t>4,76; 14,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 3,24</t>
+          <t>-1,51; 3,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 6,31</t>
+          <t>0,78; 6,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 7,38</t>
+          <t>0,49; 7,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 3,68</t>
+          <t>0,05; 3,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,49; 5,52</t>
+          <t>1,43; 5,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,64; 8,93</t>
+          <t>2,49; 8,97</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 106,39</t>
+          <t>-0,67; 114,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,63; 120,76</t>
+          <t>3,98; 118,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54,32; 236,05</t>
+          <t>55,85; 244,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-37,06; 112,8</t>
+          <t>-32,81; 109,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,08; 210,12</t>
+          <t>12,76; 217,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 252,17</t>
+          <t>9,07; 237,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 78,22</t>
+          <t>0,19; 81,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,83; 112,45</t>
+          <t>21,22; 120,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>41,34; 185,65</t>
+          <t>40,94; 190,78</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 0,91</t>
+          <t>-3,99; 1,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,71; 7,92</t>
+          <t>1,34; 7,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,62; 12,85</t>
+          <t>5,5; 13,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 0,97</t>
+          <t>-2,03; 1,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 4,55</t>
+          <t>0,28; 4,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,48; 5,72</t>
+          <t>1,65; 5,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 0,57</t>
+          <t>-2,52; 0,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,79; 5,56</t>
+          <t>1,94; 5,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,84; 8,31</t>
+          <t>4,05; 8,81</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-53,75; 20,46</t>
+          <t>-51,93; 23,56</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21,18; 157,72</t>
+          <t>15,65; 159,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>68,79; 270,39</t>
+          <t>66,83; 267,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-69,93; 83,34</t>
+          <t>-68,61; 86,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,72; 324,23</t>
+          <t>4,87; 287,79</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38,64; 409,78</t>
+          <t>56,2; 413,94</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-50,1; 19,14</t>
+          <t>-50,16; 14,5</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>35,58; 169,41</t>
+          <t>39,93; 176,51</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>78,55; 253,51</t>
+          <t>79,97; 259,47</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 5,88</t>
+          <t>-0,86; 5,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,24; 10,79</t>
+          <t>3,12; 10,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 15,74</t>
+          <t>-1,29; 15,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 2,58</t>
+          <t>-2,81; 2,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 3,42</t>
+          <t>-1,96; 3,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 4,48</t>
+          <t>-0,51; 4,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 3,3</t>
+          <t>-0,91; 3,35</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 5,96</t>
+          <t>1,57; 6,03</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,62; 8,73</t>
+          <t>1,26; 9,04</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-11,49; 136,04</t>
+          <t>-14,47; 131,93</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>37,15; 247,19</t>
+          <t>36,47; 235,11</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-10,21; 299,41</t>
+          <t>4,2; 312,53</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-45,29; 77,59</t>
+          <t>-45,26; 74,7</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-32,61; 96,38</t>
+          <t>-34,32; 102,44</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-9,28; 127,55</t>
+          <t>-7,92; 135,16</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-14,72; 73,16</t>
+          <t>-13,79; 77,11</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>21,09; 137,41</t>
+          <t>24,54; 142,94</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>24,65; 191,21</t>
+          <t>29,99; 194,41</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 3,59</t>
+          <t>-3,67; 3,82</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,92; 8,77</t>
+          <t>0,73; 8,5</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,76; 17,37</t>
+          <t>8,52; 16,71</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 3,82</t>
+          <t>-4,04; 4,03</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,19; 11,35</t>
+          <t>2,15; 10,89</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,05; 11,64</t>
+          <t>4,43; 11,87</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 2,7</t>
+          <t>-2,81; 2,56</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,33; 8,65</t>
+          <t>2,61; 8,39</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,97; 13,28</t>
+          <t>7,72; 13,39</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-41,17; 73,65</t>
+          <t>-41,37; 79,59</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>6,7; 170,04</t>
+          <t>5,67; 167,7</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>88,6; 352,47</t>
+          <t>87,72; 340,71</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-37,08; 57,7</t>
+          <t>-38,64; 55,69</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>17,19; 165,14</t>
+          <t>19,73; 165,81</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>35,9; 179,15</t>
+          <t>38,64; 180,99</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-29,62; 40,35</t>
+          <t>-29,65; 39,78</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>23,55; 133,01</t>
+          <t>27,69; 126,85</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>85,06; 209,86</t>
+          <t>80,09; 207,17</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 8,21</t>
+          <t>-2,12; 7,61</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1,92; 12,24</t>
+          <t>1,22; 11,91</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7,59; 17,25</t>
+          <t>6,91; 17,15</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 8,27</t>
+          <t>-3,99; 8,35</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 9,07</t>
+          <t>-3,36; 9,24</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-14,74; 13,02</t>
+          <t>-14,84; 13,09</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 6,19</t>
+          <t>-2,1; 6,51</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,07; 8,89</t>
+          <t>0,08; 8,6</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 12,91</t>
+          <t>-4,95; 12,86</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-22,85; 117,22</t>
+          <t>-18,64; 106,86</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>14,32; 185,56</t>
+          <t>6,25; 167,56</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>59,55; 254,86</t>
+          <t>54,18; 251,19</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-18,66; 44,28</t>
+          <t>-16,62; 43,41</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-12,41; 48,89</t>
+          <t>-14,02; 47,85</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-59,0; 63,73</t>
+          <t>-54,72; 62,86</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-11,79; 45,4</t>
+          <t>-11,15; 46,18</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0,34; 64,86</t>
+          <t>0,27; 63,22</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-26,85; 85,73</t>
+          <t>-27,23; 84,1</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 10,05</t>
+          <t>-6,29; 9,52</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 13,37</t>
+          <t>-1,32; 13,05</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3,43; 17,4</t>
+          <t>3,97; 17,47</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 10,19</t>
+          <t>-3,92; 11,1</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 13,62</t>
+          <t>-1,81; 14,11</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,4; 27,91</t>
+          <t>15,5; 28,27</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 8,43</t>
+          <t>-3,23; 7,97</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 11,64</t>
+          <t>0,84; 12,24</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>12,4; 21,83</t>
+          <t>12,46; 21,79</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-23,2; 56,89</t>
+          <t>-26,97; 57,94</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 82,37</t>
+          <t>-4,92; 76,75</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>13,03; 109,02</t>
+          <t>15,9; 108,42</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-11,29; 34,32</t>
+          <t>-10,26; 37,42</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 44,99</t>
+          <t>-5,16; 46,41</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>39,63; 95,3</t>
+          <t>39,58; 97,79</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-8,78; 32,61</t>
+          <t>-9,95; 30,69</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 45,58</t>
+          <t>1,91; 46,55</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>38,25; 84,6</t>
+          <t>38,16; 85,51</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 2,47</t>
+          <t>-0,31; 2,54</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3,83; 6,94</t>
+          <t>3,6; 6,66</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>5,45; 11,56</t>
+          <t>5,65; 11,61</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 2,59</t>
+          <t>-0,2; 2,8</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2,91; 6,0</t>
+          <t>2,95; 6,03</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,28; 9,3</t>
+          <t>4,24; 9,26</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,07; 2,06</t>
+          <t>0,14; 2,17</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>3,75; 5,85</t>
+          <t>3,78; 5,89</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>6,19; 9,98</t>
+          <t>6,23; 9,87</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 36,48</t>
+          <t>-3,77; 37,87</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>47,33; 102,2</t>
+          <t>43,69; 99,09</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>74,99; 171,77</t>
+          <t>77,09; 173,62</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 32,41</t>
+          <t>-2,34; 33,83</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>30,85; 75,35</t>
+          <t>32,11; 76,08</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>46,84; 112,7</t>
+          <t>49,65; 113,27</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>0,53; 26,89</t>
+          <t>1,68; 28,73</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>44,27; 77,23</t>
+          <t>44,08; 77,76</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>74,99; 130,52</t>
+          <t>75,34; 128,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P1_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P1_R-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>2,79</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,01</t>
+          <t>2,91</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,56</t>
+          <t>2,87</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,53; -0,22</t>
+          <t>-4,57; -0,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,13; 6,85</t>
+          <t>0,25; 6,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 6,45</t>
+          <t>-0,96; 8,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,11; 4,72</t>
+          <t>-0,08; 4,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,8; 8,81</t>
+          <t>2,89; 8,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 6,75</t>
+          <t>0,29; 7,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 1,49</t>
+          <t>-1,78; 1,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,35; 6,64</t>
+          <t>2,25; 6,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 5,23</t>
+          <t>0,32; 5,8</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>166,77%</t>
+          <t>160,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>101,42%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-87,08; 1,08</t>
+          <t>-87,3; -4,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 255,24</t>
+          <t>-1,33; 248,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-64,8; 269,44</t>
+          <t>-26,17; 295,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 433,86</t>
+          <t>-18,12; 400,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>93,72; 869,8</t>
+          <t>91,94; 877,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,0; 550,64</t>
+          <t>4,49; 690,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-48,71; 71,09</t>
+          <t>-51,79; 68,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>59,94; 326,53</t>
+          <t>56,52; 308,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-20,58; 224,34</t>
+          <t>1,98; 255,45</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8,99</t>
+          <t>8,9</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,92</t>
+          <t>4,89</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5,95</t>
+          <t>6,68</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,01; 6,17</t>
+          <t>-0,36; 6,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 6,91</t>
+          <t>0,49; 7,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,76; 14,21</t>
+          <t>4,66; 13,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 3,18</t>
+          <t>-1,68; 3,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 6,08</t>
+          <t>0,91; 5,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 7,33</t>
+          <t>2,25; 8,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 3,92</t>
+          <t>-0,16; 3,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,43; 5,64</t>
+          <t>1,3; 5,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,49; 8,97</t>
+          <t>4,02; 9,51</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>128,64%</t>
+          <t>127,38%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>101,01%</t>
+          <t>125,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>106,89%</t>
+          <t>120,11%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 114,57</t>
+          <t>-5,03; 104,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,98; 118,7</t>
+          <t>4,24; 124,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55,85; 244,53</t>
+          <t>53,64; 242,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-32,81; 109,14</t>
+          <t>-34,84; 105,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,76; 217,65</t>
+          <t>16,46; 226,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,07; 237,27</t>
+          <t>36,91; 282,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 81,89</t>
+          <t>-3,16; 83,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,22; 120,89</t>
+          <t>19,08; 117,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>40,94; 190,78</t>
+          <t>62,62; 196,69</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9,26</t>
+          <t>9,68</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>3,68</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6,24</t>
+          <t>6,75</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 1,04</t>
+          <t>-4,41; 0,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,34; 7,67</t>
+          <t>1,26; 7,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,5; 13,42</t>
+          <t>5,86; 13,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 1,01</t>
+          <t>-1,91; 0,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 4,11</t>
+          <t>0,57; 4,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,65; 5,65</t>
+          <t>1,79; 5,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 0,45</t>
+          <t>-2,36; 0,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,94; 5,64</t>
+          <t>1,76; 5,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,05; 8,81</t>
+          <t>4,72; 8,95</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>148,97%</t>
+          <t>155,6%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>169,5%</t>
+          <t>175,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>153,12%</t>
+          <t>165,57%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-51,93; 23,56</t>
+          <t>-57,37; 13,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15,65; 159,01</t>
+          <t>14,65; 163,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>66,83; 267,16</t>
+          <t>70,23; 273,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-68,61; 86,48</t>
+          <t>-71,14; 71,83</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,87; 287,79</t>
+          <t>13,47; 321,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>56,2; 413,94</t>
+          <t>53,73; 433,33</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-50,16; 14,5</t>
+          <t>-47,94; 19,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>39,93; 176,51</t>
+          <t>35,82; 170,44</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>79,97; 259,47</t>
+          <t>95,8; 278,8</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8,78</t>
+          <t>14,56</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,09</t>
+          <t>2,61</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5,87</t>
+          <t>8,42</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 5,83</t>
+          <t>-0,7; 5,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,12; 10,78</t>
+          <t>3,16; 10,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 15,9</t>
+          <t>10,14; 18,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 2,49</t>
+          <t>-2,7; 2,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 3,5</t>
+          <t>-2,24; 3,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 4,52</t>
+          <t>0,12; 5,13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 3,35</t>
+          <t>-0,85; 3,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,57; 6,03</t>
+          <t>1,41; 6,02</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,26; 9,04</t>
+          <t>5,97; 10,54</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>143,85%</t>
+          <t>238,61%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>107,6%</t>
+          <t>154,31%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-14,47; 131,93</t>
+          <t>-11,94; 125,37</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>36,47; 235,11</t>
+          <t>35,69; 219,07</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,2; 312,53</t>
+          <t>123,95; 394,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-45,26; 74,7</t>
+          <t>-42,04; 75,49</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-34,32; 102,44</t>
+          <t>-35,26; 96,9</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 135,16</t>
+          <t>0,53; 153,43</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-13,79; 77,11</t>
+          <t>-13,95; 76,72</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>24,54; 142,94</t>
+          <t>17,87; 133,35</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>29,99; 194,41</t>
+          <t>88,88; 244,07</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12,97</t>
+          <t>12,95</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,31</t>
+          <t>8,02</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>10,64</t>
+          <t>10,46</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 3,82</t>
+          <t>-3,94; 3,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,73; 8,5</t>
+          <t>0,5; 8,86</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,52; 16,71</t>
+          <t>9,27; 17,06</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 4,03</t>
+          <t>-4,11; 3,66</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,15; 10,89</t>
+          <t>2,48; 11,02</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,43; 11,87</t>
+          <t>4,36; 11,26</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 2,56</t>
+          <t>-2,42; 3,05</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,61; 8,39</t>
+          <t>2,61; 8,83</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,72; 13,39</t>
+          <t>7,64; 13,22</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>187,55%</t>
+          <t>187,15%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>135,66%</t>
+          <t>133,42%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-41,37; 79,59</t>
+          <t>-44,31; 68,68</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>5,67; 167,7</t>
+          <t>3,53; 181,73</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>87,72; 340,71</t>
+          <t>98,98; 356,88</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-38,64; 55,69</t>
+          <t>-38,32; 55,97</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>19,73; 165,81</t>
+          <t>21,12; 155,62</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>38,64; 180,99</t>
+          <t>37,34; 166,43</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-29,65; 39,78</t>
+          <t>-26,87; 47,54</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>27,69; 126,85</t>
+          <t>28,56; 135,48</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>80,09; 207,17</t>
+          <t>80,35; 206,19</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12,5</t>
+          <t>12,33</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,01</t>
+          <t>10,94</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5,76</t>
+          <t>11,35</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 7,61</t>
+          <t>-2,61; 8,03</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1,22; 11,91</t>
+          <t>1,78; 12,62</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6,91; 17,15</t>
+          <t>7,26; 17,04</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 8,35</t>
+          <t>-4,23; 8,23</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 9,24</t>
+          <t>-2,77; 9,95</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-14,84; 13,09</t>
+          <t>5,84; 15,99</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 6,51</t>
+          <t>-1,8; 7,16</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,08; 8,6</t>
+          <t>0,27; 8,55</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 12,86</t>
+          <t>7,86; 15,45</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>134,28%</t>
+          <t>132,46%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>70,65%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-18,64; 106,86</t>
+          <t>-25,29; 110,06</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>6,25; 167,56</t>
+          <t>12,02; 172,15</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>54,18; 251,19</t>
+          <t>57,36; 270,28</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-16,62; 43,41</t>
+          <t>-16,91; 45,74</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-14,02; 47,85</t>
+          <t>-10,78; 53,11</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-54,72; 62,86</t>
+          <t>23,26; 87,76</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-11,15; 46,18</t>
+          <t>-9,93; 52,46</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0,27; 63,22</t>
+          <t>1,57; 61,65</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-27,23; 84,1</t>
+          <t>42,09; 110,54</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10,75</t>
+          <t>10,35</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>21,89</t>
+          <t>21,79</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>17,27</t>
+          <t>17,01</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 9,52</t>
+          <t>-4,97; 10,49</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 13,05</t>
+          <t>-1,87; 12,77</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3,97; 17,47</t>
+          <t>2,85; 17,12</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 11,1</t>
+          <t>-4,56; 11,0</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 14,11</t>
+          <t>-1,23; 14,89</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,5; 28,27</t>
+          <t>15,32; 28,03</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 7,97</t>
+          <t>-3,07; 7,9</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,84; 12,24</t>
+          <t>0,81; 11,69</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>12,46; 21,79</t>
+          <t>12,6; 21,74</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>58,87%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-26,97; 57,94</t>
+          <t>-21,52; 61,79</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 76,75</t>
+          <t>-7,37; 77,56</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>15,9; 108,42</t>
+          <t>10,67; 107,89</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-10,26; 37,42</t>
+          <t>-11,96; 37,74</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 46,41</t>
+          <t>-3,23; 52,32</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>39,58; 97,79</t>
+          <t>38,75; 95,85</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-9,95; 30,69</t>
+          <t>-9,57; 30,33</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>1,91; 46,55</t>
+          <t>2,55; 45,56</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>38,16; 85,51</t>
+          <t>38,59; 85,87</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>9,46</t>
+          <t>11,14</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>7,47</t>
+          <t>8,83</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>8,44</t>
+          <t>9,96</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 2,54</t>
+          <t>-0,24; 2,48</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3,6; 6,66</t>
+          <t>3,81; 6,81</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>5,65; 11,61</t>
+          <t>9,58; 12,84</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 2,8</t>
+          <t>-0,2; 2,7</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2,95; 6,03</t>
+          <t>2,98; 5,98</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,24; 9,26</t>
+          <t>7,38; 10,18</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,14; 2,17</t>
+          <t>0,16; 2,12</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>3,78; 5,89</t>
+          <t>3,7; 6,01</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>6,23; 9,87</t>
+          <t>8,86; 10,98</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>129,92%</t>
+          <t>152,99%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>100,78%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>105,1%</t>
+          <t>124,02%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 37,87</t>
+          <t>-3,37; 37,52</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>43,69; 99,09</t>
+          <t>47,44; 103,41</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>77,09; 173,62</t>
+          <t>120,91; 200,07</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 33,83</t>
+          <t>-2,48; 33,63</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>32,11; 76,08</t>
+          <t>31,07; 74,0</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>49,65; 113,27</t>
+          <t>77,37; 127,83</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,68; 28,73</t>
+          <t>1,79; 28,32</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>44,08; 77,76</t>
+          <t>42,87; 79,5</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>75,34; 128,64</t>
+          <t>103,32; 145,53</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P1_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P1_R-Edad-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales</t>
+          <t>Población que conforma un hogar unipersonal</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
